--- a/data/Example/model_inputs/Input_data_example.xlsx
+++ b/data/Example/model_inputs/Input_data_example.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:101_{93367A34-0ECE-48D8-82EC-F57212DB67C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:101_{93367A34-0ECE-48D8-82EC-F57212DB67C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D95C25B0-C80E-4044-ABD0-2A5A066D974D}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_base_case" sheetId="79" r:id="rId1"/>
@@ -2092,7 +2092,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="279">
   <si>
     <t>Red: Don't change the name without changing the Julia code</t>
   </si>
@@ -2809,9 +2809,6 @@
   </si>
   <si>
     <t>https://backend.orbit.dtu.dk/ws/portalfiles/portal/264043718/MarE_Fuel_LCOE_and_optimal_electricity_supply_strategies_for_P2X_plants.pdf</t>
-  </si>
-  <si>
-    <t>Investment (EUR/Capacity installed)2025 bench</t>
   </si>
   <si>
     <t>Water supply (desalination plant)</t>
@@ -3931,16 +3928,16 @@
         <v>108</v>
       </c>
       <c r="G1" s="49" t="s">
+        <v>260</v>
+      </c>
+      <c r="H1" s="49" t="s">
         <v>261</v>
-      </c>
-      <c r="H1" s="49" t="s">
-        <v>262</v>
       </c>
       <c r="I1" s="49" t="s">
         <v>120</v>
       </c>
       <c r="J1" s="50" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="K1" s="126" t="s">
         <v>2</v>
@@ -3982,7 +3979,7 @@
         <v>140</v>
       </c>
       <c r="X1" s="52" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="Y1" s="52" t="s">
         <v>141</v>
@@ -4183,7 +4180,7 @@
         <v>Used (1 or 0)All</v>
       </c>
       <c r="G4" s="15" t="str">
-        <f t="shared" ref="G4:H4" si="17">G2&amp;G3</f>
+        <f t="shared" ref="G4:AA4" si="17">G2&amp;G3</f>
         <v>Capacity unitsAll</v>
       </c>
       <c r="H4" s="15" t="str">
@@ -4191,78 +4188,79 @@
         <v>Output unitsAll</v>
       </c>
       <c r="I4" s="15" t="str">
-        <f>I2&amp;I3</f>
+        <f t="shared" si="17"/>
         <v>Unit tagAll</v>
       </c>
       <c r="J4" s="15" t="str">
-        <f t="shared" ref="J4:O4" si="18">J2&amp;J3</f>
+        <f t="shared" si="17"/>
         <v>Yearly demand (output)All</v>
       </c>
-      <c r="K4" s="127" t="str">
-        <f t="shared" si="18"/>
+      <c r="K4" s="15" t="str">
+        <f t="shared" si="17"/>
         <v>Produced fromAll</v>
       </c>
       <c r="L4" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>El balanceAll</v>
       </c>
       <c r="M4" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>Heat balanceAll</v>
       </c>
       <c r="N4" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>H2 balanceAll</v>
       </c>
       <c r="O4" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>Max CapacityAll</v>
       </c>
       <c r="P4" s="15" t="str">
-        <f t="shared" ref="P4:U4" si="19">P2&amp;P3</f>
+        <f t="shared" si="17"/>
         <v>Fuel production rate (kg output/kg input)2025</v>
       </c>
       <c r="Q4" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>Heat generated (kWh/output)2025</v>
       </c>
       <c r="R4" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>Load min (% of max capacity)2025</v>
       </c>
       <c r="S4" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>Ramp up (% of capacity /h)2025</v>
       </c>
       <c r="T4" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>Ramp down (% of capacity /h)2025</v>
       </c>
       <c r="U4" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>Electrical consumption (kWh/output)2025</v>
       </c>
-      <c r="V4" s="15" t="s">
-        <v>239</v>
+      <c r="V4" s="15" t="str">
+        <f t="shared" si="17"/>
+        <v>Investment (EUR/Capacity installed)2025</v>
       </c>
       <c r="W4" s="15" t="str">
-        <f t="shared" ref="W4:AA4" si="20">W2&amp;W3</f>
+        <f t="shared" si="17"/>
         <v>Fixed cost (EUR/Capacity installed/y)2025</v>
       </c>
       <c r="X4" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="17"/>
         <v>Variable cost (EUR/output)2025</v>
       </c>
       <c r="Y4" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="17"/>
         <v>Fuel selling price (EUR/output)2025</v>
       </c>
       <c r="Z4" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="17"/>
         <v>Fuel buying price (EUR/output)2025</v>
       </c>
       <c r="AA4" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="17"/>
         <v>Annuity factor2025</v>
       </c>
     </row>
@@ -4274,35 +4272,35 @@
         <v>10</v>
       </c>
       <c r="F5" s="8">
-        <f t="shared" ref="F5:O5" si="21">COLUMN(F2)-COLUMN($E$5)</f>
+        <f t="shared" ref="F5:O5" si="18">COLUMN(F2)-COLUMN($E$5)</f>
         <v>1</v>
       </c>
       <c r="G5" s="8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>2</v>
       </c>
       <c r="H5" s="8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>3</v>
       </c>
       <c r="I5" s="8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>4</v>
       </c>
       <c r="J5" s="8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>5</v>
       </c>
       <c r="K5" s="128">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>6</v>
       </c>
       <c r="L5" s="8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>7</v>
       </c>
       <c r="M5" s="8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>8</v>
       </c>
       <c r="N5" s="8">
@@ -4310,54 +4308,54 @@
         <v>9</v>
       </c>
       <c r="O5" s="8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>10</v>
       </c>
       <c r="P5" s="8">
-        <f t="shared" ref="P5:U5" si="22">COLUMN(P2)-COLUMN($E$5)</f>
+        <f t="shared" ref="P5:U5" si="19">COLUMN(P2)-COLUMN($E$5)</f>
         <v>11</v>
       </c>
       <c r="Q5" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="19"/>
         <v>12</v>
       </c>
       <c r="R5" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="19"/>
         <v>13</v>
       </c>
       <c r="S5" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="19"/>
         <v>14</v>
       </c>
       <c r="T5" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="19"/>
         <v>15</v>
       </c>
       <c r="U5" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="19"/>
         <v>16</v>
       </c>
       <c r="V5" s="8">
         <v>17</v>
       </c>
       <c r="W5" s="8">
-        <f t="shared" ref="W5:AA5" si="23">COLUMN(W2)-COLUMN($E$5)</f>
+        <f t="shared" ref="W5:AA5" si="20">COLUMN(W2)-COLUMN($E$5)</f>
         <v>18</v>
       </c>
       <c r="X5" s="8">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>19</v>
       </c>
       <c r="Y5" s="8">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>20</v>
       </c>
       <c r="Z5" s="8">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>21</v>
       </c>
       <c r="AA5" s="8">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>22</v>
       </c>
     </row>
@@ -4375,17 +4373,17 @@
         <v>67</v>
       </c>
       <c r="E6" s="9">
-        <f t="shared" ref="E6:E42" si="24">ROW(D6)-ROW($E$5)</f>
+        <f t="shared" ref="E6:E42" si="21">ROW(D6)-ROW($E$5)</f>
         <v>1</v>
       </c>
       <c r="F6" s="69">
         <v>1</v>
       </c>
       <c r="G6" s="69" t="s">
+        <v>272</v>
+      </c>
+      <c r="H6" s="69" t="s">
         <v>273</v>
-      </c>
-      <c r="H6" s="69" t="s">
-        <v>274</v>
       </c>
       <c r="I6" s="69" t="s">
         <v>76</v>
@@ -4458,17 +4456,17 @@
         <v>82</v>
       </c>
       <c r="E7" s="9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>2</v>
       </c>
       <c r="F7" s="69">
         <v>1</v>
       </c>
       <c r="G7" s="69" t="s">
+        <v>272</v>
+      </c>
+      <c r="H7" s="69" t="s">
         <v>273</v>
-      </c>
-      <c r="H7" s="69" t="s">
-        <v>274</v>
       </c>
       <c r="I7" s="69" t="s">
         <v>77</v>
@@ -4539,20 +4537,20 @@
         <v>135</v>
       </c>
       <c r="D8" s="68" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E8" s="9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>3</v>
       </c>
       <c r="F8" s="69">
         <v>1</v>
       </c>
       <c r="G8" s="69" t="s">
+        <v>274</v>
+      </c>
+      <c r="H8" s="69" t="s">
         <v>275</v>
-      </c>
-      <c r="H8" s="69" t="s">
-        <v>276</v>
       </c>
       <c r="I8" s="69" t="s">
         <v>88</v>
@@ -4624,20 +4622,20 @@
         <v>135</v>
       </c>
       <c r="D9" s="78" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E9" s="9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>4</v>
       </c>
       <c r="F9" s="79">
         <v>1</v>
       </c>
       <c r="G9" s="79" t="s">
+        <v>276</v>
+      </c>
+      <c r="H9" s="79" t="s">
         <v>277</v>
-      </c>
-      <c r="H9" s="79" t="s">
-        <v>278</v>
       </c>
       <c r="I9" s="79" t="s">
         <v>78</v>
@@ -4698,7 +4696,7 @@
         <v>0</v>
       </c>
       <c r="AA9" s="95">
-        <f t="shared" ref="AA9:AA10" si="25">1/11.3</f>
+        <f t="shared" ref="AA9:AA10" si="22">1/11.3</f>
         <v>8.8495575221238937E-2</v>
       </c>
     </row>
@@ -4711,7 +4709,7 @@
         <v>135</v>
       </c>
       <c r="D10" s="78" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E10" s="9">
         <f>ROW(D10)-ROW($E$5)</f>
@@ -4721,10 +4719,10 @@
         <v>1</v>
       </c>
       <c r="G10" s="79" t="s">
+        <v>276</v>
+      </c>
+      <c r="H10" s="79" t="s">
         <v>277</v>
-      </c>
-      <c r="H10" s="79" t="s">
-        <v>278</v>
       </c>
       <c r="I10" s="79" t="s">
         <v>79</v>
@@ -4786,7 +4784,7 @@
         <v>0</v>
       </c>
       <c r="AA10" s="95">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>8.8495575221238937E-2</v>
       </c>
     </row>
@@ -4799,7 +4797,7 @@
         <v>135</v>
       </c>
       <c r="D11" s="84" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E11" s="9">
         <f>ROW(D11)-ROW($E$5)</f>
@@ -4809,10 +4807,10 @@
         <v>1</v>
       </c>
       <c r="G11" s="85" t="s">
+        <v>264</v>
+      </c>
+      <c r="H11" s="85" t="s">
         <v>265</v>
-      </c>
-      <c r="H11" s="85" t="s">
-        <v>266</v>
       </c>
       <c r="I11" s="85" t="s">
         <v>184</v>
@@ -4883,20 +4881,20 @@
         <v>188</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E12" s="9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>7</v>
       </c>
       <c r="F12" s="2">
         <v>1</v>
       </c>
       <c r="G12" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="H12" s="2" t="s">
         <v>271</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>272</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>176</v>
@@ -4969,17 +4967,17 @@
         <v>177</v>
       </c>
       <c r="E13" s="9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>8</v>
       </c>
       <c r="F13" s="99">
         <v>1</v>
       </c>
       <c r="G13" s="99" t="s">
+        <v>264</v>
+      </c>
+      <c r="H13" s="99" t="s">
         <v>265</v>
-      </c>
-      <c r="H13" s="99" t="s">
-        <v>266</v>
       </c>
       <c r="I13" s="99" t="s">
         <v>80</v>
@@ -5004,7 +5002,7 @@
         <v>20000</v>
       </c>
       <c r="P13" s="100">
-        <f t="shared" ref="P13:P14" si="26">(1/9)*0.8</f>
+        <f t="shared" ref="P13:P14" si="23">(1/9)*0.8</f>
         <v>8.8888888888888892E-2</v>
       </c>
       <c r="Q13" s="100">
@@ -5039,7 +5037,7 @@
         <v>0</v>
       </c>
       <c r="AA13" s="103">
-        <f t="shared" ref="AA13:AA14" si="27">1/11.3</f>
+        <f t="shared" ref="AA13:AA14" si="24">1/11.3</f>
         <v>8.8495575221238937E-2</v>
       </c>
     </row>
@@ -5055,17 +5053,17 @@
         <v>180</v>
       </c>
       <c r="E14" s="9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>9</v>
       </c>
       <c r="F14" s="107">
         <v>1</v>
       </c>
       <c r="G14" s="107" t="s">
+        <v>264</v>
+      </c>
+      <c r="H14" s="107" t="s">
         <v>265</v>
-      </c>
-      <c r="H14" s="107" t="s">
-        <v>266</v>
       </c>
       <c r="I14" s="107" t="s">
         <v>181</v>
@@ -5091,7 +5089,7 @@
         <v>20000</v>
       </c>
       <c r="P14" s="108">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>8.8888888888888892E-2</v>
       </c>
       <c r="Q14" s="108">
@@ -5126,7 +5124,7 @@
         <v>0</v>
       </c>
       <c r="AA14" s="112">
-        <f t="shared" si="27"/>
+        <f t="shared" si="24"/>
         <v>8.8495575221238937E-2</v>
       </c>
     </row>
@@ -5142,17 +5140,17 @@
         <v>65</v>
       </c>
       <c r="E15" s="9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>10</v>
       </c>
       <c r="F15" s="2">
         <v>1</v>
       </c>
       <c r="G15" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="H15" s="2" t="s">
         <v>265</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>266</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>66</v>
@@ -5225,17 +5223,17 @@
         <v>29</v>
       </c>
       <c r="E16" s="9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>11</v>
       </c>
       <c r="F16" s="2">
         <v>1</v>
       </c>
       <c r="G16" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="H16" s="2" t="s">
         <v>265</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>266</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>18</v>
@@ -5305,20 +5303,20 @@
         <v>188</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E17" s="9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>12</v>
       </c>
       <c r="F17" s="2">
         <v>1</v>
       </c>
       <c r="G17" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="H17" s="2" t="s">
         <v>265</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>266</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>185</v>
@@ -5391,17 +5389,17 @@
         <v>30</v>
       </c>
       <c r="E18" s="9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>13</v>
       </c>
       <c r="F18" s="92">
         <v>1</v>
       </c>
       <c r="G18" s="92" t="s">
+        <v>266</v>
+      </c>
+      <c r="H18" s="92" t="s">
         <v>267</v>
-      </c>
-      <c r="H18" s="92" t="s">
-        <v>268</v>
       </c>
       <c r="I18" s="92" t="s">
         <v>19</v>
@@ -5468,23 +5466,23 @@
         <v>27</v>
       </c>
       <c r="C19" s="132" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D19" s="91" t="s">
         <v>31</v>
       </c>
       <c r="E19" s="9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>14</v>
       </c>
       <c r="F19" s="92">
         <v>1</v>
       </c>
       <c r="G19" s="92" t="s">
+        <v>266</v>
+      </c>
+      <c r="H19" s="92" t="s">
         <v>267</v>
-      </c>
-      <c r="H19" s="92" t="s">
-        <v>268</v>
       </c>
       <c r="I19" s="92" t="s">
         <v>20</v>
@@ -5551,23 +5549,23 @@
         <v>111</v>
       </c>
       <c r="C20" s="132" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D20" s="91" t="s">
         <v>32</v>
       </c>
       <c r="E20" s="9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>15</v>
       </c>
       <c r="F20" s="92">
         <v>1</v>
       </c>
       <c r="G20" s="92" t="s">
+        <v>268</v>
+      </c>
+      <c r="H20" s="92" t="s">
         <v>269</v>
-      </c>
-      <c r="H20" s="92" t="s">
-        <v>270</v>
       </c>
       <c r="I20" s="92" t="s">
         <v>13</v>
@@ -5638,20 +5636,20 @@
         <v>188</v>
       </c>
       <c r="D21" s="117" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E21" s="9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>16</v>
       </c>
       <c r="F21" s="62">
         <v>1</v>
       </c>
       <c r="G21" s="62" t="s">
+        <v>264</v>
+      </c>
+      <c r="H21" s="62" t="s">
         <v>265</v>
-      </c>
-      <c r="H21" s="62" t="s">
-        <v>266</v>
       </c>
       <c r="I21" s="62" t="s">
         <v>129</v>
@@ -5720,20 +5718,20 @@
         <v>188</v>
       </c>
       <c r="D22" s="117" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E22" s="9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>17</v>
       </c>
       <c r="F22" s="62">
         <v>1</v>
       </c>
       <c r="G22" s="62" t="s">
+        <v>264</v>
+      </c>
+      <c r="H22" s="62" t="s">
         <v>265</v>
-      </c>
-      <c r="H22" s="62" t="s">
-        <v>266</v>
       </c>
       <c r="I22" s="62" t="s">
         <v>130</v>
@@ -5802,20 +5800,20 @@
         <v>188</v>
       </c>
       <c r="D23" s="120" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E23" s="116">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>18</v>
       </c>
       <c r="F23" s="121">
         <v>1</v>
       </c>
       <c r="G23" s="121" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H23" s="121" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I23" s="121" t="s">
         <v>131</v>
@@ -5890,17 +5888,17 @@
         <v>37</v>
       </c>
       <c r="E24" s="9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>19</v>
       </c>
       <c r="F24" s="2">
         <v>1</v>
       </c>
       <c r="G24" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="H24" s="2" t="s">
         <v>263</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>264</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>38</v>
@@ -5979,10 +5977,10 @@
         <v>1</v>
       </c>
       <c r="G25" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="H25" s="2" t="s">
         <v>263</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>264</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>40</v>
@@ -6003,7 +6001,7 @@
         <v>0</v>
       </c>
       <c r="O25">
-        <f t="shared" ref="O25:O38" si="28">$O$24</f>
+        <f t="shared" ref="O25:O38" si="25">$O$24</f>
         <v>2000000</v>
       </c>
       <c r="P25" s="10">
@@ -6056,17 +6054,17 @@
         <v>132</v>
       </c>
       <c r="E26" s="9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>21</v>
       </c>
       <c r="F26" s="2">
         <v>1</v>
       </c>
       <c r="G26" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="H26" s="2" t="s">
         <v>263</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>264</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>43</v>
@@ -6087,7 +6085,7 @@
         <v>0</v>
       </c>
       <c r="O26">
-        <f t="shared" si="28"/>
+        <f t="shared" si="25"/>
         <v>2000000</v>
       </c>
       <c r="P26" s="10">
@@ -6130,7 +6128,7 @@
     <row r="27" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A27" s="136"/>
       <c r="B27" s="12" t="str">
-        <f t="shared" ref="B27:B37" si="29">CONCATENATE("RPU_"&amp;D27)</f>
+        <f t="shared" ref="B27:B37" si="26">CONCATENATE("RPU_"&amp;D27)</f>
         <v>RPU_ON_SP198-HH150</v>
       </c>
       <c r="C27" s="11" t="s">
@@ -6140,17 +6138,17 @@
         <v>44</v>
       </c>
       <c r="E27" s="9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>22</v>
       </c>
       <c r="F27" s="2">
         <v>1</v>
       </c>
       <c r="G27" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="H27" s="2" t="s">
         <v>263</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>264</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>45</v>
@@ -6171,7 +6169,7 @@
         <v>0</v>
       </c>
       <c r="O27">
-        <f t="shared" si="28"/>
+        <f t="shared" si="25"/>
         <v>2000000</v>
       </c>
       <c r="P27" s="10">
@@ -6214,7 +6212,7 @@
     <row r="28" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A28" s="136"/>
       <c r="B28" s="12" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="26"/>
         <v>RPU_ON_SP237-HH100</v>
       </c>
       <c r="C28" s="11" t="s">
@@ -6224,17 +6222,17 @@
         <v>46</v>
       </c>
       <c r="E28" s="9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>23</v>
       </c>
       <c r="F28" s="2">
         <v>1</v>
       </c>
       <c r="G28" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="H28" s="2" t="s">
         <v>263</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>264</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>47</v>
@@ -6255,7 +6253,7 @@
         <v>0</v>
       </c>
       <c r="O28">
-        <f t="shared" si="28"/>
+        <f t="shared" si="25"/>
         <v>2000000</v>
       </c>
       <c r="P28" s="10">
@@ -6298,7 +6296,7 @@
     <row r="29" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A29" s="136"/>
       <c r="B29" s="12" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="26"/>
         <v>RPU_ON_SP237-HH150</v>
       </c>
       <c r="C29" s="11" t="s">
@@ -6308,17 +6306,17 @@
         <v>48</v>
       </c>
       <c r="E29" s="9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>24</v>
       </c>
       <c r="F29" s="2">
         <v>1</v>
       </c>
       <c r="G29" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="H29" s="2" t="s">
         <v>263</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>264</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>49</v>
@@ -6339,7 +6337,7 @@
         <v>0</v>
       </c>
       <c r="O29">
-        <f t="shared" si="28"/>
+        <f t="shared" si="25"/>
         <v>2000000</v>
       </c>
       <c r="P29" s="10">
@@ -6382,7 +6380,7 @@
     <row r="30" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A30" s="136"/>
       <c r="B30" s="12" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="26"/>
         <v>RPU_ON_SP277-HH100</v>
       </c>
       <c r="C30" s="11" t="s">
@@ -6392,17 +6390,17 @@
         <v>50</v>
       </c>
       <c r="E30" s="9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>25</v>
       </c>
       <c r="F30" s="2">
         <v>1</v>
       </c>
       <c r="G30" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="H30" s="2" t="s">
         <v>263</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>264</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>51</v>
@@ -6423,7 +6421,7 @@
         <v>0</v>
       </c>
       <c r="O30">
-        <f t="shared" si="28"/>
+        <f t="shared" si="25"/>
         <v>2000000</v>
       </c>
       <c r="P30" s="10">
@@ -6466,7 +6464,7 @@
     <row r="31" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A31" s="136"/>
       <c r="B31" s="12" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="26"/>
         <v>RPU_ON_SP277-HH150</v>
       </c>
       <c r="C31" s="11" t="s">
@@ -6476,17 +6474,17 @@
         <v>52</v>
       </c>
       <c r="E31" s="9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>26</v>
       </c>
       <c r="F31" s="2">
         <v>1</v>
       </c>
       <c r="G31" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="H31" s="2" t="s">
         <v>263</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>264</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>53</v>
@@ -6507,7 +6505,7 @@
         <v>0</v>
       </c>
       <c r="O31">
-        <f t="shared" si="28"/>
+        <f t="shared" si="25"/>
         <v>2000000</v>
       </c>
       <c r="P31" s="10">
@@ -6550,7 +6548,7 @@
     <row r="32" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A32" s="136"/>
       <c r="B32" s="12" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="26"/>
         <v>RPU_ON_SP321-HH100</v>
       </c>
       <c r="C32" s="11" t="s">
@@ -6560,17 +6558,17 @@
         <v>54</v>
       </c>
       <c r="E32" s="9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>27</v>
       </c>
       <c r="F32" s="2">
         <v>1</v>
       </c>
       <c r="G32" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="H32" s="2" t="s">
         <v>263</v>
-      </c>
-      <c r="H32" s="2" t="s">
-        <v>264</v>
       </c>
       <c r="I32" s="2" t="s">
         <v>55</v>
@@ -6591,7 +6589,7 @@
         <v>0</v>
       </c>
       <c r="O32">
-        <f t="shared" si="28"/>
+        <f t="shared" si="25"/>
         <v>2000000</v>
       </c>
       <c r="P32" s="10">
@@ -6634,7 +6632,7 @@
     <row r="33" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A33" s="136"/>
       <c r="B33" s="12" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="26"/>
         <v>RPU_ON_SP321-HH150</v>
       </c>
       <c r="C33" s="11" t="s">
@@ -6644,17 +6642,17 @@
         <v>56</v>
       </c>
       <c r="E33" s="9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>28</v>
       </c>
       <c r="F33" s="2">
         <v>1</v>
       </c>
       <c r="G33" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="H33" s="2" t="s">
         <v>263</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>264</v>
       </c>
       <c r="I33" s="2" t="s">
         <v>57</v>
@@ -6675,7 +6673,7 @@
         <v>0</v>
       </c>
       <c r="O33">
-        <f t="shared" si="28"/>
+        <f t="shared" si="25"/>
         <v>2000000</v>
       </c>
       <c r="P33" s="10">
@@ -6718,7 +6716,7 @@
     <row r="34" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A34" s="136"/>
       <c r="B34" s="12" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="26"/>
         <v>RPU_OFF_SP379-HH100</v>
       </c>
       <c r="C34" s="11" t="s">
@@ -6728,17 +6726,17 @@
         <v>58</v>
       </c>
       <c r="E34" s="9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>29</v>
       </c>
       <c r="F34" s="2">
         <v>1</v>
       </c>
       <c r="G34" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="H34" s="2" t="s">
         <v>263</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>264</v>
       </c>
       <c r="I34" s="2" t="s">
         <v>59</v>
@@ -6759,7 +6757,7 @@
         <v>0</v>
       </c>
       <c r="O34">
-        <f t="shared" si="28"/>
+        <f t="shared" si="25"/>
         <v>2000000</v>
       </c>
       <c r="P34" s="10">
@@ -6802,7 +6800,7 @@
     <row r="35" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A35" s="136"/>
       <c r="B35" s="12" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="26"/>
         <v>RPU_OFF_SP379-HH150</v>
       </c>
       <c r="C35" s="11" t="s">
@@ -6812,17 +6810,17 @@
         <v>60</v>
       </c>
       <c r="E35" s="9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>30</v>
       </c>
       <c r="F35" s="2">
         <v>1</v>
       </c>
       <c r="G35" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="H35" s="2" t="s">
         <v>263</v>
-      </c>
-      <c r="H35" s="2" t="s">
-        <v>264</v>
       </c>
       <c r="I35" s="2" t="s">
         <v>61</v>
@@ -6843,7 +6841,7 @@
         <v>0</v>
       </c>
       <c r="O35">
-        <f t="shared" si="28"/>
+        <f t="shared" si="25"/>
         <v>2000000</v>
       </c>
       <c r="P35" s="10">
@@ -6886,7 +6884,7 @@
     <row r="36" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A36" s="136"/>
       <c r="B36" s="12" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="26"/>
         <v>RPU_OFF_SP450-HH100</v>
       </c>
       <c r="C36" s="11" t="s">
@@ -6896,17 +6894,17 @@
         <v>62</v>
       </c>
       <c r="E36" s="9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>31</v>
       </c>
       <c r="F36" s="2">
         <v>1</v>
       </c>
       <c r="G36" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="H36" s="2" t="s">
         <v>263</v>
-      </c>
-      <c r="H36" s="2" t="s">
-        <v>264</v>
       </c>
       <c r="I36" s="2" t="s">
         <v>63</v>
@@ -6927,7 +6925,7 @@
         <v>0</v>
       </c>
       <c r="O36">
-        <f t="shared" si="28"/>
+        <f t="shared" si="25"/>
         <v>2000000</v>
       </c>
       <c r="P36" s="10">
@@ -6970,7 +6968,7 @@
     <row r="37" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A37" s="136"/>
       <c r="B37" s="12" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="26"/>
         <v>RPU_OFF_SP450-HH150</v>
       </c>
       <c r="C37" s="11" t="s">
@@ -6980,17 +6978,17 @@
         <v>133</v>
       </c>
       <c r="E37" s="9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>32</v>
       </c>
       <c r="F37" s="2">
         <v>1</v>
       </c>
       <c r="G37" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="H37" s="2" t="s">
         <v>263</v>
-      </c>
-      <c r="H37" s="2" t="s">
-        <v>264</v>
       </c>
       <c r="I37" s="2" t="s">
         <v>64</v>
@@ -7011,7 +7009,7 @@
         <v>0</v>
       </c>
       <c r="O37">
-        <f t="shared" si="28"/>
+        <f t="shared" si="25"/>
         <v>2000000</v>
       </c>
       <c r="P37" s="10">
@@ -7063,17 +7061,17 @@
         <v>33</v>
       </c>
       <c r="E38" s="9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>33</v>
       </c>
       <c r="F38" s="2">
         <v>1</v>
       </c>
       <c r="G38" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="H38" s="2" t="s">
         <v>263</v>
-      </c>
-      <c r="H38" s="2" t="s">
-        <v>264</v>
       </c>
       <c r="I38" s="2" t="s">
         <v>21</v>
@@ -7094,7 +7092,7 @@
         <v>0</v>
       </c>
       <c r="O38">
-        <f t="shared" si="28"/>
+        <f t="shared" si="25"/>
         <v>2000000</v>
       </c>
       <c r="P38" s="10">
@@ -7146,17 +7144,17 @@
         <v>189</v>
       </c>
       <c r="E39" s="9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>34</v>
       </c>
       <c r="F39" s="2">
         <v>1</v>
       </c>
       <c r="G39" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="H39" s="2" t="s">
         <v>263</v>
-      </c>
-      <c r="H39" s="2" t="s">
-        <v>264</v>
       </c>
       <c r="I39" s="2" t="s">
         <v>189</v>
@@ -7228,17 +7226,17 @@
         <v>34</v>
       </c>
       <c r="E40" s="9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>35</v>
       </c>
       <c r="F40" s="2">
         <v>1</v>
       </c>
       <c r="G40" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="H40" s="2" t="s">
         <v>263</v>
-      </c>
-      <c r="H40" s="2" t="s">
-        <v>264</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>22</v>
@@ -7311,17 +7309,17 @@
         <v>35</v>
       </c>
       <c r="E41" s="9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>36</v>
       </c>
       <c r="F41" s="2">
         <v>1</v>
       </c>
       <c r="G41" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="H41" s="2" t="s">
         <v>263</v>
-      </c>
-      <c r="H41" s="2" t="s">
-        <v>264</v>
       </c>
       <c r="I41" s="2" t="s">
         <v>23</v>
@@ -7394,17 +7392,17 @@
         <v>36</v>
       </c>
       <c r="E42" s="9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>37</v>
       </c>
       <c r="F42" s="2">
         <v>1</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="I42" s="2" t="s">
         <v>24</v>
@@ -9184,7 +9182,7 @@
     </row>
     <row r="2" spans="1:140" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="4" spans="1:140" s="16" customFormat="1" x14ac:dyDescent="0.35">
@@ -9756,7 +9754,7 @@
         <v>171</v>
       </c>
       <c r="C6" s="42" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D6" s="42" t="str">
         <f>Data_base_case!$R$1</f>
@@ -9782,7 +9780,7 @@
         <v>171</v>
       </c>
       <c r="C7" s="42" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D7" s="42" t="str">
         <f>Data_base_case!$R$1</f>
@@ -9837,7 +9835,7 @@
         <v>136</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D9" s="29" t="str">
         <f>Data_base_case!$R$1</f>
@@ -9863,7 +9861,7 @@
         <v>136</v>
       </c>
       <c r="C10" s="29" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D10" s="29" t="str">
         <f>Data_base_case!$R$1</f>
@@ -9888,7 +9886,7 @@
         <v>125</v>
       </c>
       <c r="C11" s="23" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D11" s="23" t="str">
         <f>Data_base_case!$R$1</f>
@@ -9914,7 +9912,7 @@
         <v>125</v>
       </c>
       <c r="C12" s="23" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D12" s="23" t="str">
         <f>Data_base_case!$R$1</f>
@@ -9942,7 +9940,7 @@
         <v>172</v>
       </c>
       <c r="C13" s="44" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D13" s="44" t="str">
         <f>Data_base_case!$R$1</f>
@@ -9967,7 +9965,7 @@
         <v>172</v>
       </c>
       <c r="C14" s="44" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D14" s="44" t="str">
         <f>Data_base_case!$R$1</f>
@@ -10037,7 +10035,7 @@
         <v>128</v>
       </c>
       <c r="C2" s="141" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>186</v>
@@ -10187,7 +10185,7 @@
         <v>1</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C8" s="14" t="s">
         <v>124</v>
@@ -10215,7 +10213,7 @@
         <v>175</v>
       </c>
       <c r="K8" s="17" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="L8" t="b">
         <v>0</v>
@@ -10242,7 +10240,7 @@
         <v>2</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C9" s="14" t="s">
         <v>124</v>
@@ -10270,7 +10268,7 @@
         <v>175</v>
       </c>
       <c r="K9" s="17" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="L9" t="b">
         <v>0</v>
@@ -10297,7 +10295,7 @@
         <v>3</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C10" s="14" t="s">
         <v>124</v>
@@ -10325,7 +10323,7 @@
         <v>175</v>
       </c>
       <c r="K10" s="17" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="L10" t="b">
         <v>0</v>
@@ -10352,7 +10350,7 @@
         <v>4</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C11" s="14" t="s">
         <v>170</v>
@@ -10380,7 +10378,7 @@
         <v>175</v>
       </c>
       <c r="K11" s="17" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="L11" t="b">
         <v>0</v>
@@ -10407,7 +10405,7 @@
         <v>5</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C12" s="14" t="s">
         <v>170</v>
@@ -10435,7 +10433,7 @@
         <v>175</v>
       </c>
       <c r="K12" s="17" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="L12" t="b">
         <v>0</v>
@@ -10462,7 +10460,7 @@
         <v>6</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C13" s="14" t="s">
         <v>170</v>
@@ -10490,7 +10488,7 @@
         <v>175</v>
       </c>
       <c r="K13" s="17" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="L13" t="b">
         <v>0</v>
@@ -10517,7 +10515,7 @@
         <v>7</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C14" s="14" t="s">
         <v>170</v>
@@ -10545,7 +10543,7 @@
         <v>175</v>
       </c>
       <c r="K14" s="17" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="L14" t="b">
         <v>0</v>
@@ -10572,7 +10570,7 @@
         <v>8</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C15" s="14" t="s">
         <v>170</v>
@@ -10600,7 +10598,7 @@
         <v>175</v>
       </c>
       <c r="K15" s="17" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="L15" t="b">
         <v>0</v>
@@ -10627,7 +10625,7 @@
         <v>9</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C16" s="14" t="s">
         <v>170</v>
@@ -10655,7 +10653,7 @@
         <v>175</v>
       </c>
       <c r="K16" s="17" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="L16" t="b">
         <v>0</v>
@@ -10682,7 +10680,7 @@
         <v>10</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C17" s="14" t="s">
         <v>170</v>
@@ -10710,7 +10708,7 @@
         <v>175</v>
       </c>
       <c r="K17" s="17" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="L17" t="b">
         <v>0</v>
@@ -10737,7 +10735,7 @@
         <v>11</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C18" s="14" t="s">
         <v>170</v>
@@ -10765,7 +10763,7 @@
         <v>175</v>
       </c>
       <c r="K18" s="17" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="L18" t="b">
         <v>0</v>
@@ -10792,7 +10790,7 @@
         <v>12</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C19" s="14" t="s">
         <v>170</v>
@@ -10820,7 +10818,7 @@
         <v>175</v>
       </c>
       <c r="K19" s="17" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="L19" t="b">
         <v>0</v>
@@ -10847,7 +10845,7 @@
         <v>13</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C20" s="14" t="s">
         <v>136</v>
@@ -10875,7 +10873,7 @@
         <v>175</v>
       </c>
       <c r="K20" s="17" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="L20" t="b">
         <v>0</v>
@@ -10902,7 +10900,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C21" s="14" t="s">
         <v>136</v>
@@ -10930,7 +10928,7 @@
         <v>175</v>
       </c>
       <c r="K21" s="17" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="L21" t="b">
         <v>0</v>
@@ -10957,7 +10955,7 @@
         <v>15</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C22" s="14" t="s">
         <v>136</v>
@@ -10985,7 +10983,7 @@
         <v>175</v>
       </c>
       <c r="K22" s="17" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="L22" t="b">
         <v>0</v>
@@ -11012,7 +11010,7 @@
         <v>16</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C23" s="14" t="s">
         <v>125</v>
@@ -11040,7 +11038,7 @@
         <v>175</v>
       </c>
       <c r="K23" s="17" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="L23" t="b">
         <v>0</v>
@@ -11067,7 +11065,7 @@
         <v>17</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C24" s="14" t="s">
         <v>125</v>
@@ -11095,7 +11093,7 @@
         <v>175</v>
       </c>
       <c r="K24" s="17" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="L24" t="b">
         <v>0</v>
@@ -11122,7 +11120,7 @@
         <v>18</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C25" s="14" t="s">
         <v>125</v>
@@ -11150,7 +11148,7 @@
         <v>175</v>
       </c>
       <c r="K25" s="17" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="L25" t="b">
         <v>0</v>
@@ -11177,7 +11175,7 @@
         <v>19</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C26" s="14" t="s">
         <v>172</v>
@@ -11205,7 +11203,7 @@
         <v>175</v>
       </c>
       <c r="K26" s="17" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="L26" t="b">
         <v>0</v>
@@ -11232,7 +11230,7 @@
         <v>20</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C27" s="14" t="s">
         <v>172</v>
@@ -11260,7 +11258,7 @@
         <v>175</v>
       </c>
       <c r="K27" s="17" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="L27" t="b">
         <v>0</v>
@@ -11287,7 +11285,7 @@
         <v>21</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C28" s="14" t="s">
         <v>172</v>
@@ -11315,7 +11313,7 @@
         <v>175</v>
       </c>
       <c r="K28" s="17" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="L28" t="b">
         <v>0</v>
@@ -11403,7 +11401,7 @@
         <v>190</v>
       </c>
       <c r="C2" s="54" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D2" s="54">
         <v>2023</v>

--- a/data/Example/model_inputs/Input_data_example.xlsx
+++ b/data/Example/model_inputs/Input_data_example.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:101_{93367A34-0ECE-48D8-82EC-F57212DB67C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D95C25B0-C80E-4044-ABD0-2A5A066D974D}"/>
+  <xr:revisionPtr revIDLastSave="22" documentId="13_ncr:101_{93367A34-0ECE-48D8-82EC-F57212DB67C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{672E4ECE-399D-4FFB-A185-A5835BD2803B}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19090" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_base_case" sheetId="79" r:id="rId1"/>
@@ -2092,7 +2092,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="673" uniqueCount="279">
   <si>
     <t>Red: Don't change the name without changing the Julia code</t>
   </si>
@@ -2217,9 +2217,6 @@
     <t>Solar_tracking</t>
   </si>
   <si>
-    <t>RPU_Solar_track</t>
-  </si>
-  <si>
     <t>RPU_Solar_fixed</t>
   </si>
   <si>
@@ -2929,6 +2926,9 @@
   </si>
   <si>
     <t>Yearly demand (output)</t>
+  </si>
+  <si>
+    <t>RPU_Solar_tracking</t>
   </si>
 </sst>
 </file>
@@ -3482,6 +3482,15 @@
     </xf>
     <xf numFmtId="1" fontId="5" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3494,15 +3503,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3553,6 +3553,9 @@
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Sources"/>
       <sheetName val="Fuel production cost"/>
@@ -3623,6 +3626,10 @@
     </sheetDataSet>
   </externalBook>
 </externalLink>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3917,27 +3924,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="134" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="134"/>
-      <c r="C1" s="134"/>
-      <c r="D1" s="134"/>
-      <c r="E1" s="135"/>
+      <c r="A1" s="137" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="137"/>
+      <c r="C1" s="137"/>
+      <c r="D1" s="137"/>
+      <c r="E1" s="138"/>
       <c r="F1" s="49" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G1" s="49" t="s">
+        <v>259</v>
+      </c>
+      <c r="H1" s="49" t="s">
         <v>260</v>
       </c>
-      <c r="H1" s="49" t="s">
-        <v>261</v>
-      </c>
       <c r="I1" s="49" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="J1" s="50" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="K1" s="126" t="s">
         <v>2</v>
@@ -3955,51 +3962,51 @@
         <v>6</v>
       </c>
       <c r="P1" s="52" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q1" s="52" t="s">
         <v>68</v>
       </c>
-      <c r="Q1" s="52" t="s">
+      <c r="R1" s="52" t="s">
         <v>69</v>
       </c>
-      <c r="R1" s="52" t="s">
+      <c r="S1" s="52" t="s">
         <v>70</v>
       </c>
-      <c r="S1" s="52" t="s">
+      <c r="T1" s="52" t="s">
         <v>71</v>
       </c>
-      <c r="T1" s="52" t="s">
+      <c r="U1" s="52" t="s">
         <v>72</v>
       </c>
-      <c r="U1" s="52" t="s">
+      <c r="V1" s="52" t="s">
+        <v>138</v>
+      </c>
+      <c r="W1" s="52" t="s">
+        <v>139</v>
+      </c>
+      <c r="X1" s="52" t="s">
+        <v>257</v>
+      </c>
+      <c r="Y1" s="52" t="s">
+        <v>140</v>
+      </c>
+      <c r="Z1" s="52" t="s">
+        <v>141</v>
+      </c>
+      <c r="AA1" s="51" t="s">
         <v>73</v>
-      </c>
-      <c r="V1" s="52" t="s">
-        <v>139</v>
-      </c>
-      <c r="W1" s="52" t="s">
-        <v>140</v>
-      </c>
-      <c r="X1" s="52" t="s">
-        <v>258</v>
-      </c>
-      <c r="Y1" s="52" t="s">
-        <v>141</v>
-      </c>
-      <c r="Z1" s="52" t="s">
-        <v>142</v>
-      </c>
-      <c r="AA1" s="51" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:27" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="31"/>
-      <c r="B2" s="137" t="s">
+      <c r="B2" s="140" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="138" t="s">
+      <c r="C2" s="141" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="137" t="s">
+      <c r="D2" s="140" t="s">
         <v>9</v>
       </c>
       <c r="E2" s="36" t="s">
@@ -4096,41 +4103,41 @@
     </row>
     <row r="3" spans="1:27" s="6" customFormat="1" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="35"/>
-      <c r="B3" s="137"/>
-      <c r="C3" s="138"/>
-      <c r="D3" s="137"/>
+      <c r="B3" s="140"/>
+      <c r="C3" s="141"/>
+      <c r="D3" s="140"/>
       <c r="E3" s="36" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="I3" s="15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J3" s="15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K3" s="127" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L3" s="15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M3" s="15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="N3" s="14" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O3" s="15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="P3" s="3">
         <v>2025</v>
@@ -4171,9 +4178,9 @@
     </row>
     <row r="4" spans="1:27" s="6" customFormat="1" ht="5.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="35"/>
-      <c r="B4" s="137"/>
-      <c r="C4" s="138"/>
-      <c r="D4" s="137"/>
+      <c r="B4" s="140"/>
+      <c r="C4" s="141"/>
+      <c r="D4" s="140"/>
       <c r="E4" s="36"/>
       <c r="F4" s="15" t="str">
         <f>F2&amp;F3</f>
@@ -4265,9 +4272,9 @@
       </c>
     </row>
     <row r="5" spans="1:27" s="8" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="137"/>
-      <c r="C5" s="138"/>
-      <c r="D5" s="137"/>
+      <c r="B5" s="140"/>
+      <c r="C5" s="141"/>
+      <c r="D5" s="140"/>
       <c r="E5" s="53" t="s">
         <v>10</v>
       </c>
@@ -4360,17 +4367,17 @@
       </c>
     </row>
     <row r="6" spans="1:27" s="70" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="136" t="s">
+      <c r="A6" s="139" t="s">
         <v>11</v>
       </c>
       <c r="B6" s="66" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C6" s="67" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D6" s="68" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E6" s="9">
         <f t="shared" ref="E6:E42" si="21">ROW(D6)-ROW($E$5)</f>
@@ -4380,13 +4387,13 @@
         <v>1</v>
       </c>
       <c r="G6" s="69" t="s">
+        <v>271</v>
+      </c>
+      <c r="H6" s="69" t="s">
         <v>272</v>
       </c>
-      <c r="H6" s="69" t="s">
-        <v>273</v>
-      </c>
       <c r="I6" s="69" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J6" s="70">
         <v>0</v>
@@ -4404,8 +4411,8 @@
       <c r="N6" s="70">
         <v>0</v>
       </c>
-      <c r="O6" s="70">
-        <v>40000</v>
+      <c r="O6" s="69" t="s">
+        <v>101</v>
       </c>
       <c r="P6" s="70">
         <v>1.37</v>
@@ -4445,15 +4452,15 @@
       </c>
     </row>
     <row r="7" spans="1:27" s="70" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="136"/>
+      <c r="A7" s="139"/>
       <c r="B7" s="66" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C7" s="67" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D7" s="68" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E7" s="9">
         <f t="shared" si="21"/>
@@ -4463,13 +4470,13 @@
         <v>1</v>
       </c>
       <c r="G7" s="69" t="s">
+        <v>271</v>
+      </c>
+      <c r="H7" s="69" t="s">
         <v>272</v>
       </c>
-      <c r="H7" s="69" t="s">
-        <v>273</v>
-      </c>
       <c r="I7" s="69" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J7" s="70">
         <v>0</v>
@@ -4487,9 +4494,8 @@
       <c r="N7" s="70">
         <v>0</v>
       </c>
-      <c r="O7" s="70">
-        <f>O6</f>
-        <v>40000</v>
+      <c r="O7" s="69" t="s">
+        <v>101</v>
       </c>
       <c r="P7" s="70">
         <v>1.37</v>
@@ -4529,15 +4535,15 @@
       </c>
     </row>
     <row r="8" spans="1:27" s="70" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="136"/>
+      <c r="A8" s="139"/>
       <c r="B8" s="66" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C8" s="75" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D8" s="68" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E8" s="9">
         <f t="shared" si="21"/>
@@ -4547,13 +4553,13 @@
         <v>1</v>
       </c>
       <c r="G8" s="69" t="s">
+        <v>273</v>
+      </c>
+      <c r="H8" s="69" t="s">
         <v>274</v>
       </c>
-      <c r="H8" s="69" t="s">
-        <v>275</v>
-      </c>
       <c r="I8" s="69" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J8" s="133">
         <f>(2.2/(19.9/3.6))*10^9</f>
@@ -4572,8 +4578,8 @@
       <c r="N8" s="70">
         <v>0</v>
       </c>
-      <c r="O8" s="70">
-        <v>20000</v>
+      <c r="O8" s="69" t="s">
+        <v>101</v>
       </c>
       <c r="P8" s="70">
         <v>5.26</v>
@@ -4614,15 +4620,15 @@
       </c>
     </row>
     <row r="9" spans="1:27" s="81" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="136"/>
+      <c r="A9" s="139"/>
       <c r="B9" s="76" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C9" s="77" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D9" s="78" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E9" s="9">
         <f t="shared" si="21"/>
@@ -4632,13 +4638,13 @@
         <v>1</v>
       </c>
       <c r="G9" s="79" t="s">
+        <v>275</v>
+      </c>
+      <c r="H9" s="79" t="s">
         <v>276</v>
       </c>
-      <c r="H9" s="79" t="s">
-        <v>277</v>
-      </c>
       <c r="I9" s="79" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J9" s="133">
         <f>(2.2/(18.6/3.6))*10^9</f>
@@ -4657,8 +4663,8 @@
       <c r="N9" s="81">
         <v>0</v>
       </c>
-      <c r="O9" s="81">
-        <v>20000</v>
+      <c r="O9" s="79" t="s">
+        <v>101</v>
       </c>
       <c r="P9" s="124">
         <f>1/0.18</f>
@@ -4701,15 +4707,15 @@
       </c>
     </row>
     <row r="10" spans="1:27" s="81" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="136"/>
+      <c r="A10" s="139"/>
       <c r="B10" s="76" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C10" s="77" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D10" s="78" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E10" s="9">
         <f>ROW(D10)-ROW($E$5)</f>
@@ -4719,13 +4725,13 @@
         <v>1</v>
       </c>
       <c r="G10" s="79" t="s">
+        <v>275</v>
+      </c>
+      <c r="H10" s="79" t="s">
         <v>276</v>
       </c>
-      <c r="H10" s="79" t="s">
-        <v>277</v>
-      </c>
       <c r="I10" s="79" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J10" s="133">
         <f>(2.2/(18.6/3.6))*10^9</f>
@@ -4744,9 +4750,8 @@
       <c r="N10" s="81">
         <v>0</v>
       </c>
-      <c r="O10" s="81">
-        <f>O9</f>
-        <v>20000</v>
+      <c r="O10" s="79" t="s">
+        <v>101</v>
       </c>
       <c r="P10" s="124">
         <f>1/0.18</f>
@@ -4789,15 +4794,15 @@
       </c>
     </row>
     <row r="11" spans="1:27" s="86" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="136"/>
+      <c r="A11" s="139"/>
       <c r="B11" s="83" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C11" s="113" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D11" s="84" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E11" s="9">
         <f>ROW(D11)-ROW($E$5)</f>
@@ -4807,20 +4812,20 @@
         <v>1</v>
       </c>
       <c r="G11" s="85" t="s">
+        <v>263</v>
+      </c>
+      <c r="H11" s="85" t="s">
         <v>264</v>
       </c>
-      <c r="H11" s="85" t="s">
-        <v>265</v>
-      </c>
       <c r="I11" s="85" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="J11" s="133">
         <f>(2.2/(120/3.6))*10^9</f>
         <v>66000000</v>
       </c>
       <c r="K11" s="87" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="L11" s="86">
         <v>0</v>
@@ -4831,9 +4836,8 @@
       <c r="N11" s="86">
         <v>0</v>
       </c>
-      <c r="O11" s="86">
-        <f>O10</f>
-        <v>20000</v>
+      <c r="O11" s="85" t="s">
+        <v>101</v>
       </c>
       <c r="P11" s="86">
         <v>1</v>
@@ -4873,15 +4877,15 @@
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A12" s="136"/>
+      <c r="A12" s="139"/>
       <c r="B12" s="19" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E12" s="9">
         <f t="shared" si="21"/>
@@ -4891,13 +4895,13 @@
         <v>1</v>
       </c>
       <c r="G12" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="H12" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="H12" s="2" t="s">
-        <v>271</v>
-      </c>
       <c r="I12" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -4914,8 +4918,8 @@
       <c r="N12">
         <v>0</v>
       </c>
-      <c r="O12">
-        <v>400000</v>
+      <c r="O12" s="2" t="s">
+        <v>101</v>
       </c>
       <c r="P12">
         <v>0</v>
@@ -4956,15 +4960,15 @@
       </c>
     </row>
     <row r="13" spans="1:27" s="100" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="136"/>
+      <c r="A13" s="139"/>
       <c r="B13" s="96" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C13" s="97" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D13" s="98" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E13" s="9">
         <f t="shared" si="21"/>
@@ -4974,13 +4978,13 @@
         <v>1</v>
       </c>
       <c r="G13" s="99" t="s">
+        <v>263</v>
+      </c>
+      <c r="H13" s="99" t="s">
         <v>264</v>
       </c>
-      <c r="H13" s="99" t="s">
-        <v>265</v>
-      </c>
       <c r="I13" s="99" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J13" s="100">
         <v>0</v>
@@ -4998,8 +5002,8 @@
       <c r="N13" s="100">
         <v>1</v>
       </c>
-      <c r="O13" s="100">
-        <v>20000</v>
+      <c r="O13" s="99" t="s">
+        <v>101</v>
       </c>
       <c r="P13" s="100">
         <f t="shared" ref="P13:P14" si="23">(1/9)*0.8</f>
@@ -5042,15 +5046,15 @@
       </c>
     </row>
     <row r="14" spans="1:27" s="108" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="136"/>
+      <c r="A14" s="139"/>
       <c r="B14" s="104" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C14" s="105" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D14" s="106" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E14" s="9">
         <f t="shared" si="21"/>
@@ -5060,13 +5064,13 @@
         <v>1</v>
       </c>
       <c r="G14" s="107" t="s">
+        <v>263</v>
+      </c>
+      <c r="H14" s="107" t="s">
         <v>264</v>
       </c>
-      <c r="H14" s="107" t="s">
-        <v>265</v>
-      </c>
       <c r="I14" s="107" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="J14" s="108">
         <v>0</v>
@@ -5084,9 +5088,8 @@
       <c r="N14" s="108">
         <v>1</v>
       </c>
-      <c r="O14" s="108">
-        <f>O13</f>
-        <v>20000</v>
+      <c r="O14" s="107" t="s">
+        <v>101</v>
       </c>
       <c r="P14" s="108">
         <f t="shared" si="23"/>
@@ -5129,15 +5132,15 @@
       </c>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A15" s="136"/>
+      <c r="A15" s="139"/>
       <c r="B15" s="19" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E15" s="9">
         <f t="shared" si="21"/>
@@ -5147,13 +5150,13 @@
         <v>1</v>
       </c>
       <c r="G15" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="H15" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="H15" s="2" t="s">
-        <v>265</v>
-      </c>
       <c r="I15" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J15" s="10">
         <v>0</v>
@@ -5170,9 +5173,8 @@
       <c r="N15">
         <v>-1</v>
       </c>
-      <c r="O15">
-        <f>O13</f>
-        <v>20000</v>
+      <c r="O15" s="2" t="s">
+        <v>101</v>
       </c>
       <c r="P15" s="10">
         <v>0</v>
@@ -5212,12 +5214,12 @@
       </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A16" s="136"/>
+      <c r="A16" s="139"/>
       <c r="B16" s="19" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>29</v>
@@ -5230,10 +5232,10 @@
         <v>1</v>
       </c>
       <c r="G16" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="H16" s="2" t="s">
         <v>264</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>265</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>18</v>
@@ -5253,9 +5255,8 @@
       <c r="N16">
         <v>-1</v>
       </c>
-      <c r="O16">
-        <f>O13</f>
-        <v>20000</v>
+      <c r="O16" s="2" t="s">
+        <v>101</v>
       </c>
       <c r="P16" s="48">
         <v>0</v>
@@ -5295,15 +5296,15 @@
       </c>
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A17" s="136"/>
+      <c r="A17" s="139"/>
       <c r="B17" s="19" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E17" s="9">
         <f t="shared" si="21"/>
@@ -5313,13 +5314,13 @@
         <v>1</v>
       </c>
       <c r="G17" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="H17" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="H17" s="2" t="s">
-        <v>265</v>
-      </c>
       <c r="I17" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="J17" s="48">
         <v>0</v>
@@ -5336,9 +5337,8 @@
       <c r="N17">
         <v>-1</v>
       </c>
-      <c r="O17">
-        <f>O14</f>
-        <v>20000</v>
+      <c r="O17" s="2" t="s">
+        <v>101</v>
       </c>
       <c r="P17" s="48">
         <v>0</v>
@@ -5378,12 +5378,12 @@
       </c>
     </row>
     <row r="18" spans="1:27" s="47" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="136"/>
+      <c r="A18" s="139"/>
       <c r="B18" s="89" t="s">
         <v>26</v>
       </c>
       <c r="C18" s="90" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D18" s="91" t="s">
         <v>30</v>
@@ -5396,10 +5396,10 @@
         <v>1</v>
       </c>
       <c r="G18" s="92" t="s">
+        <v>265</v>
+      </c>
+      <c r="H18" s="92" t="s">
         <v>266</v>
-      </c>
-      <c r="H18" s="92" t="s">
-        <v>267</v>
       </c>
       <c r="I18" s="92" t="s">
         <v>19</v>
@@ -5419,9 +5419,8 @@
       <c r="N18" s="47">
         <v>0</v>
       </c>
-      <c r="O18" s="47">
-        <f>O24</f>
-        <v>2000000</v>
+      <c r="O18" s="92" t="s">
+        <v>101</v>
       </c>
       <c r="P18" s="114">
         <v>0</v>
@@ -5461,12 +5460,12 @@
       </c>
     </row>
     <row r="19" spans="1:27" s="47" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="136"/>
+      <c r="A19" s="139"/>
       <c r="B19" s="89" t="s">
         <v>27</v>
       </c>
       <c r="C19" s="132" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D19" s="91" t="s">
         <v>31</v>
@@ -5479,10 +5478,10 @@
         <v>1</v>
       </c>
       <c r="G19" s="92" t="s">
+        <v>265</v>
+      </c>
+      <c r="H19" s="92" t="s">
         <v>266</v>
-      </c>
-      <c r="H19" s="92" t="s">
-        <v>267</v>
       </c>
       <c r="I19" s="92" t="s">
         <v>20</v>
@@ -5502,9 +5501,8 @@
       <c r="N19" s="114">
         <v>0</v>
       </c>
-      <c r="O19" s="47">
-        <f>O24</f>
-        <v>2000000</v>
+      <c r="O19" s="92" t="s">
+        <v>101</v>
       </c>
       <c r="P19" s="114">
         <v>0</v>
@@ -5544,12 +5542,12 @@
       </c>
     </row>
     <row r="20" spans="1:27" s="47" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="136"/>
+      <c r="A20" s="139"/>
       <c r="B20" s="89" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C20" s="132" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D20" s="91" t="s">
         <v>32</v>
@@ -5562,10 +5560,10 @@
         <v>1</v>
       </c>
       <c r="G20" s="92" t="s">
+        <v>267</v>
+      </c>
+      <c r="H20" s="92" t="s">
         <v>268</v>
-      </c>
-      <c r="H20" s="92" t="s">
-        <v>269</v>
       </c>
       <c r="I20" s="92" t="s">
         <v>13</v>
@@ -5586,9 +5584,8 @@
       <c r="N20" s="47">
         <v>0</v>
       </c>
-      <c r="O20" s="47">
-        <f>9*O13</f>
-        <v>180000</v>
+      <c r="O20" s="92" t="s">
+        <v>101</v>
       </c>
       <c r="P20" s="47">
         <v>8</v>
@@ -5628,15 +5625,15 @@
       </c>
     </row>
     <row r="21" spans="1:27" s="63" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="136"/>
+      <c r="A21" s="139"/>
       <c r="B21" s="60" t="s">
         <v>14</v>
       </c>
       <c r="C21" s="61" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D21" s="117" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E21" s="9">
         <f t="shared" si="21"/>
@@ -5646,13 +5643,13 @@
         <v>1</v>
       </c>
       <c r="G21" s="62" t="s">
+        <v>263</v>
+      </c>
+      <c r="H21" s="62" t="s">
         <v>264</v>
       </c>
-      <c r="H21" s="62" t="s">
-        <v>265</v>
-      </c>
       <c r="I21" s="62" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J21" s="63">
         <v>0</v>
@@ -5669,8 +5666,8 @@
       <c r="N21" s="63">
         <v>-1</v>
       </c>
-      <c r="O21" s="63">
-        <v>20000</v>
+      <c r="O21" s="62" t="s">
+        <v>101</v>
       </c>
       <c r="P21" s="65">
         <v>0</v>
@@ -5710,15 +5707,15 @@
       </c>
     </row>
     <row r="22" spans="1:27" s="63" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="136"/>
+      <c r="A22" s="139"/>
       <c r="B22" s="60" t="s">
         <v>15</v>
       </c>
       <c r="C22" s="61" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D22" s="117" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E22" s="9">
         <f t="shared" si="21"/>
@@ -5728,13 +5725,13 @@
         <v>1</v>
       </c>
       <c r="G22" s="62" t="s">
+        <v>263</v>
+      </c>
+      <c r="H22" s="62" t="s">
         <v>264</v>
       </c>
-      <c r="H22" s="62" t="s">
-        <v>265</v>
-      </c>
       <c r="I22" s="62" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J22" s="63">
         <v>0</v>
@@ -5751,8 +5748,8 @@
       <c r="N22" s="63">
         <v>1</v>
       </c>
-      <c r="O22" s="63">
-        <v>20000</v>
+      <c r="O22" s="62" t="s">
+        <v>101</v>
       </c>
       <c r="P22" s="65">
         <v>0</v>
@@ -5792,15 +5789,15 @@
       </c>
     </row>
     <row r="23" spans="1:27" s="122" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="136"/>
+      <c r="A23" s="139"/>
       <c r="B23" s="118" t="s">
         <v>16</v>
       </c>
       <c r="C23" s="119" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D23" s="120" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E23" s="116">
         <f t="shared" si="21"/>
@@ -5810,13 +5807,13 @@
         <v>1</v>
       </c>
       <c r="G23" s="121" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H23" s="121" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="I23" s="121" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="J23" s="122">
         <v>0</v>
@@ -5833,8 +5830,8 @@
       <c r="N23" s="122">
         <v>0</v>
       </c>
-      <c r="O23" s="122">
-        <v>20000000</v>
+      <c r="O23" s="121" t="s">
+        <v>101</v>
       </c>
       <c r="P23" s="122">
         <v>0</v>
@@ -5875,14 +5872,14 @@
       </c>
     </row>
     <row r="24" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="136" t="s">
+      <c r="A24" s="139" t="s">
         <v>17</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D24" s="7" t="s">
         <v>37</v>
@@ -5895,10 +5892,10 @@
         <v>1</v>
       </c>
       <c r="G24" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="H24" s="2" t="s">
         <v>262</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>263</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>38</v>
@@ -5918,8 +5915,8 @@
       <c r="N24">
         <v>0</v>
       </c>
-      <c r="O24">
-        <v>2000000</v>
+      <c r="O24" s="2" t="s">
+        <v>101</v>
       </c>
       <c r="P24" s="10">
         <v>0</v>
@@ -5959,12 +5956,12 @@
       </c>
     </row>
     <row r="25" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="136"/>
+      <c r="A25" s="139"/>
       <c r="B25" s="12" t="s">
-        <v>41</v>
+        <v>278</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D25" s="7" t="s">
         <v>39</v>
@@ -5977,10 +5974,10 @@
         <v>1</v>
       </c>
       <c r="G25" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="H25" s="2" t="s">
         <v>262</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>263</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>40</v>
@@ -6000,9 +5997,8 @@
       <c r="N25">
         <v>0</v>
       </c>
-      <c r="O25">
-        <f t="shared" ref="O25:O38" si="25">$O$24</f>
-        <v>2000000</v>
+      <c r="O25" s="2">
+        <v>50000</v>
       </c>
       <c r="P25" s="10">
         <v>0</v>
@@ -6042,16 +6038,16 @@
       </c>
     </row>
     <row r="26" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A26" s="136"/>
+      <c r="A26" s="139"/>
       <c r="B26" s="12" t="str">
         <f>CONCATENATE("RPU_"&amp;D26)</f>
         <v>RPU_ON_SP198-HH100</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E26" s="9">
         <f t="shared" si="21"/>
@@ -6061,13 +6057,13 @@
         <v>1</v>
       </c>
       <c r="G26" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="H26" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="H26" s="2" t="s">
-        <v>263</v>
-      </c>
       <c r="I26" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -6084,9 +6080,8 @@
       <c r="N26">
         <v>0</v>
       </c>
-      <c r="O26">
-        <f t="shared" si="25"/>
-        <v>2000000</v>
+      <c r="O26" s="2" t="s">
+        <v>101</v>
       </c>
       <c r="P26" s="10">
         <v>0</v>
@@ -6126,16 +6121,16 @@
       </c>
     </row>
     <row r="27" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A27" s="136"/>
+      <c r="A27" s="139"/>
       <c r="B27" s="12" t="str">
-        <f t="shared" ref="B27:B37" si="26">CONCATENATE("RPU_"&amp;D27)</f>
+        <f t="shared" ref="B27:B37" si="25">CONCATENATE("RPU_"&amp;D27)</f>
         <v>RPU_ON_SP198-HH150</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E27" s="9">
         <f t="shared" si="21"/>
@@ -6145,13 +6140,13 @@
         <v>1</v>
       </c>
       <c r="G27" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="H27" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="H27" s="2" t="s">
-        <v>263</v>
-      </c>
       <c r="I27" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -6168,9 +6163,8 @@
       <c r="N27">
         <v>0</v>
       </c>
-      <c r="O27">
-        <f t="shared" si="25"/>
-        <v>2000000</v>
+      <c r="O27" s="2" t="s">
+        <v>101</v>
       </c>
       <c r="P27" s="10">
         <v>0</v>
@@ -6210,16 +6204,16 @@
       </c>
     </row>
     <row r="28" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A28" s="136"/>
+      <c r="A28" s="139"/>
       <c r="B28" s="12" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>RPU_ON_SP237-HH100</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E28" s="9">
         <f t="shared" si="21"/>
@@ -6229,13 +6223,13 @@
         <v>1</v>
       </c>
       <c r="G28" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="H28" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="H28" s="2" t="s">
-        <v>263</v>
-      </c>
       <c r="I28" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J28">
         <v>0</v>
@@ -6252,9 +6246,8 @@
       <c r="N28">
         <v>0</v>
       </c>
-      <c r="O28">
-        <f t="shared" si="25"/>
-        <v>2000000</v>
+      <c r="O28" s="2" t="s">
+        <v>101</v>
       </c>
       <c r="P28" s="10">
         <v>0</v>
@@ -6294,16 +6287,16 @@
       </c>
     </row>
     <row r="29" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A29" s="136"/>
+      <c r="A29" s="139"/>
       <c r="B29" s="12" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>RPU_ON_SP237-HH150</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E29" s="9">
         <f t="shared" si="21"/>
@@ -6313,13 +6306,13 @@
         <v>1</v>
       </c>
       <c r="G29" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="H29" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="H29" s="2" t="s">
-        <v>263</v>
-      </c>
       <c r="I29" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J29">
         <v>0</v>
@@ -6336,9 +6329,8 @@
       <c r="N29">
         <v>0</v>
       </c>
-      <c r="O29">
-        <f t="shared" si="25"/>
-        <v>2000000</v>
+      <c r="O29" s="2" t="s">
+        <v>101</v>
       </c>
       <c r="P29" s="10">
         <v>0</v>
@@ -6378,16 +6370,16 @@
       </c>
     </row>
     <row r="30" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A30" s="136"/>
+      <c r="A30" s="139"/>
       <c r="B30" s="12" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>RPU_ON_SP277-HH100</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E30" s="9">
         <f t="shared" si="21"/>
@@ -6397,13 +6389,13 @@
         <v>1</v>
       </c>
       <c r="G30" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="H30" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="H30" s="2" t="s">
-        <v>263</v>
-      </c>
       <c r="I30" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J30">
         <v>0</v>
@@ -6420,9 +6412,8 @@
       <c r="N30">
         <v>0</v>
       </c>
-      <c r="O30">
-        <f t="shared" si="25"/>
-        <v>2000000</v>
+      <c r="O30" s="2" t="s">
+        <v>101</v>
       </c>
       <c r="P30" s="10">
         <v>0</v>
@@ -6462,16 +6453,16 @@
       </c>
     </row>
     <row r="31" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A31" s="136"/>
+      <c r="A31" s="139"/>
       <c r="B31" s="12" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>RPU_ON_SP277-HH150</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E31" s="9">
         <f t="shared" si="21"/>
@@ -6481,13 +6472,13 @@
         <v>1</v>
       </c>
       <c r="G31" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="H31" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="H31" s="2" t="s">
-        <v>263</v>
-      </c>
       <c r="I31" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J31">
         <v>0</v>
@@ -6504,9 +6495,8 @@
       <c r="N31">
         <v>0</v>
       </c>
-      <c r="O31">
-        <f t="shared" si="25"/>
-        <v>2000000</v>
+      <c r="O31" s="2" t="s">
+        <v>101</v>
       </c>
       <c r="P31" s="10">
         <v>0</v>
@@ -6546,16 +6536,16 @@
       </c>
     </row>
     <row r="32" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A32" s="136"/>
+      <c r="A32" s="139"/>
       <c r="B32" s="12" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>RPU_ON_SP321-HH100</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E32" s="9">
         <f t="shared" si="21"/>
@@ -6565,13 +6555,13 @@
         <v>1</v>
       </c>
       <c r="G32" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="H32" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="H32" s="2" t="s">
-        <v>263</v>
-      </c>
       <c r="I32" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J32">
         <v>0</v>
@@ -6588,9 +6578,8 @@
       <c r="N32">
         <v>0</v>
       </c>
-      <c r="O32">
-        <f t="shared" si="25"/>
-        <v>2000000</v>
+      <c r="O32" s="2" t="s">
+        <v>101</v>
       </c>
       <c r="P32" s="10">
         <v>0</v>
@@ -6630,16 +6619,16 @@
       </c>
     </row>
     <row r="33" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A33" s="136"/>
+      <c r="A33" s="139"/>
       <c r="B33" s="12" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>RPU_ON_SP321-HH150</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E33" s="9">
         <f t="shared" si="21"/>
@@ -6649,13 +6638,13 @@
         <v>1</v>
       </c>
       <c r="G33" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="H33" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="H33" s="2" t="s">
-        <v>263</v>
-      </c>
       <c r="I33" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J33">
         <v>0</v>
@@ -6672,9 +6661,8 @@
       <c r="N33">
         <v>0</v>
       </c>
-      <c r="O33">
-        <f t="shared" si="25"/>
-        <v>2000000</v>
+      <c r="O33" s="2" t="s">
+        <v>101</v>
       </c>
       <c r="P33" s="10">
         <v>0</v>
@@ -6714,16 +6702,16 @@
       </c>
     </row>
     <row r="34" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A34" s="136"/>
+      <c r="A34" s="139"/>
       <c r="B34" s="12" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>RPU_OFF_SP379-HH100</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E34" s="9">
         <f t="shared" si="21"/>
@@ -6733,13 +6721,13 @@
         <v>1</v>
       </c>
       <c r="G34" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="H34" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="H34" s="2" t="s">
-        <v>263</v>
-      </c>
       <c r="I34" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J34">
         <v>0</v>
@@ -6756,9 +6744,8 @@
       <c r="N34">
         <v>0</v>
       </c>
-      <c r="O34">
-        <f t="shared" si="25"/>
-        <v>2000000</v>
+      <c r="O34" s="2" t="s">
+        <v>101</v>
       </c>
       <c r="P34" s="10">
         <v>0</v>
@@ -6798,16 +6785,16 @@
       </c>
     </row>
     <row r="35" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A35" s="136"/>
+      <c r="A35" s="139"/>
       <c r="B35" s="12" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>RPU_OFF_SP379-HH150</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E35" s="9">
         <f t="shared" si="21"/>
@@ -6817,13 +6804,13 @@
         <v>1</v>
       </c>
       <c r="G35" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="H35" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="H35" s="2" t="s">
-        <v>263</v>
-      </c>
       <c r="I35" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J35">
         <v>0</v>
@@ -6840,9 +6827,8 @@
       <c r="N35">
         <v>0</v>
       </c>
-      <c r="O35">
-        <f t="shared" si="25"/>
-        <v>2000000</v>
+      <c r="O35" s="2" t="s">
+        <v>101</v>
       </c>
       <c r="P35" s="10">
         <v>0</v>
@@ -6882,16 +6868,16 @@
       </c>
     </row>
     <row r="36" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A36" s="136"/>
+      <c r="A36" s="139"/>
       <c r="B36" s="12" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>RPU_OFF_SP450-HH100</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E36" s="9">
         <f t="shared" si="21"/>
@@ -6901,13 +6887,13 @@
         <v>1</v>
       </c>
       <c r="G36" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="H36" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="H36" s="2" t="s">
-        <v>263</v>
-      </c>
       <c r="I36" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J36">
         <v>0</v>
@@ -6924,9 +6910,8 @@
       <c r="N36">
         <v>0</v>
       </c>
-      <c r="O36">
-        <f t="shared" si="25"/>
-        <v>2000000</v>
+      <c r="O36" s="2" t="s">
+        <v>101</v>
       </c>
       <c r="P36" s="10">
         <v>0</v>
@@ -6966,16 +6951,16 @@
       </c>
     </row>
     <row r="37" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A37" s="136"/>
+      <c r="A37" s="139"/>
       <c r="B37" s="12" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>RPU_OFF_SP450-HH150</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E37" s="9">
         <f t="shared" si="21"/>
@@ -6985,13 +6970,13 @@
         <v>1</v>
       </c>
       <c r="G37" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="H37" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="H37" s="2" t="s">
-        <v>263</v>
-      </c>
       <c r="I37" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J37">
         <v>0</v>
@@ -7008,9 +6993,8 @@
       <c r="N37">
         <v>0</v>
       </c>
-      <c r="O37">
-        <f t="shared" si="25"/>
-        <v>2000000</v>
+      <c r="O37" s="2" t="s">
+        <v>101</v>
       </c>
       <c r="P37" s="10">
         <v>0</v>
@@ -7050,7 +7034,7 @@
       </c>
     </row>
     <row r="38" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A38" s="136"/>
+      <c r="A38" s="139"/>
       <c r="B38" s="12" t="s">
         <v>25</v>
       </c>
@@ -7068,10 +7052,10 @@
         <v>1</v>
       </c>
       <c r="G38" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="H38" s="2" t="s">
         <v>262</v>
-      </c>
-      <c r="H38" s="2" t="s">
-        <v>263</v>
       </c>
       <c r="I38" s="2" t="s">
         <v>21</v>
@@ -7091,9 +7075,8 @@
       <c r="N38">
         <v>0</v>
       </c>
-      <c r="O38">
-        <f t="shared" si="25"/>
-        <v>2000000</v>
+      <c r="O38" s="2" t="s">
+        <v>101</v>
       </c>
       <c r="P38" s="10">
         <v>0</v>
@@ -7133,15 +7116,15 @@
       </c>
     </row>
     <row r="39" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A39" s="136"/>
+      <c r="A39" s="139"/>
       <c r="B39" s="12" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C39" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="D39" s="7" t="s">
         <v>188</v>
-      </c>
-      <c r="D39" s="7" t="s">
-        <v>189</v>
       </c>
       <c r="E39" s="9">
         <f t="shared" si="21"/>
@@ -7151,13 +7134,13 @@
         <v>1</v>
       </c>
       <c r="G39" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="H39" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="H39" s="2" t="s">
-        <v>263</v>
-      </c>
       <c r="I39" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="J39">
         <v>0</v>
@@ -7174,8 +7157,8 @@
       <c r="N39">
         <v>0</v>
       </c>
-      <c r="O39">
-        <v>24000</v>
+      <c r="O39" s="2" t="s">
+        <v>101</v>
       </c>
       <c r="P39">
         <v>0</v>
@@ -7215,12 +7198,12 @@
       </c>
     </row>
     <row r="40" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A40" s="136"/>
+      <c r="A40" s="139"/>
       <c r="B40" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D40" s="7" t="s">
         <v>34</v>
@@ -7233,10 +7216,10 @@
         <v>1</v>
       </c>
       <c r="G40" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="H40" s="2" t="s">
         <v>262</v>
-      </c>
-      <c r="H40" s="2" t="s">
-        <v>263</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>22</v>
@@ -7256,9 +7239,8 @@
       <c r="N40">
         <v>0</v>
       </c>
-      <c r="O40">
-        <f>O42/2</f>
-        <v>10000000</v>
+      <c r="O40" s="2" t="s">
+        <v>101</v>
       </c>
       <c r="P40" s="10">
         <v>0</v>
@@ -7298,12 +7280,12 @@
       </c>
     </row>
     <row r="41" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A41" s="136"/>
+      <c r="A41" s="139"/>
       <c r="B41" s="12" t="s">
         <v>15</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D41" s="7" t="s">
         <v>35</v>
@@ -7316,10 +7298,10 @@
         <v>1</v>
       </c>
       <c r="G41" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="H41" s="2" t="s">
         <v>262</v>
-      </c>
-      <c r="H41" s="2" t="s">
-        <v>263</v>
       </c>
       <c r="I41" s="2" t="s">
         <v>23</v>
@@ -7339,9 +7321,8 @@
       <c r="N41">
         <v>0</v>
       </c>
-      <c r="O41">
-        <f>3*O42</f>
-        <v>60000000</v>
+      <c r="O41" s="2" t="s">
+        <v>101</v>
       </c>
       <c r="P41" s="10">
         <v>0</v>
@@ -7381,12 +7362,12 @@
       </c>
     </row>
     <row r="42" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A42" s="136"/>
+      <c r="A42" s="139"/>
       <c r="B42" s="12" t="s">
         <v>16</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>36</v>
@@ -7399,10 +7380,10 @@
         <v>1</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="I42" s="2" t="s">
         <v>24</v>
@@ -7422,8 +7403,8 @@
       <c r="N42">
         <v>0</v>
       </c>
-      <c r="O42">
-        <v>20000000</v>
+      <c r="O42" s="2" t="s">
+        <v>101</v>
       </c>
       <c r="P42" s="10">
         <v>0</v>
@@ -7500,105 +7481,105 @@
     <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" s="14"/>
       <c r="B1" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="K1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" s="14"/>
       <c r="B2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D3" t="s">
+        <v>101</v>
+      </c>
+      <c r="E3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G3" t="s">
         <v>103</v>
       </c>
-      <c r="C3" t="s">
-        <v>102</v>
-      </c>
-      <c r="D3" t="s">
-        <v>102</v>
-      </c>
-      <c r="E3" t="s">
-        <v>81</v>
-      </c>
-      <c r="F3" t="s">
-        <v>81</v>
-      </c>
-      <c r="G3" t="s">
-        <v>104</v>
-      </c>
       <c r="H3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" s="4"/>
       <c r="B4" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C4" t="str">
         <f t="shared" ref="C4:K4" si="0">C1&amp;"_"&amp;C2&amp;"_"&amp;C3</f>
@@ -9177,38 +9158,38 @@
   <sheetData>
     <row r="1" spans="1:140" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="2" spans="1:140" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="4" spans="1:140" s="16" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A4" s="31" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F4" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="G4" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="H4" s="16" t="s">
         <v>85</v>
-      </c>
-      <c r="G4" s="16" t="s">
-        <v>116</v>
-      </c>
-      <c r="H4" s="16" t="s">
-        <v>86</v>
       </c>
       <c r="N4" s="16" t="str">
         <f>Data_base_case!F2&amp;Data_base_case!F3</f>
@@ -9722,7 +9703,7 @@
     <row r="5" spans="1:140" s="16" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="39"/>
       <c r="B5" s="16" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C5" s="16" t="s">
         <v>33</v>
@@ -9732,13 +9713,13 @@
         <v>Used (1 or 0)</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F5" s="16">
         <v>1</v>
       </c>
       <c r="G5" s="40" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H5" s="16">
         <f>INDEX(Data_base_case!$D$5:$AA$88,MATCH(Scenarios_definition!C5,Data_base_case!$D$5:$D$88,0),MATCH(Scenarios_definition!D5&amp;Scenarios_definition!G5,Data_base_case!$D$4:$AA$4,0))</f>
@@ -9751,17 +9732,17 @@
         <v>Semi-islanded</v>
       </c>
       <c r="B6" s="42" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C6" s="42" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D6" s="42" t="str">
         <f>Data_base_case!$R$1</f>
         <v>Load min (% of max capacity)</v>
       </c>
       <c r="E6" s="42" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F6" s="42">
         <v>0</v>
@@ -9777,17 +9758,17 @@
     <row r="7" spans="1:140" s="16" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="39"/>
       <c r="B7" s="42" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C7" s="42" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D7" s="42" t="str">
         <f>Data_base_case!$R$1</f>
         <v>Load min (% of max capacity)</v>
       </c>
       <c r="E7" s="42" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F7" s="42">
         <v>0</v>
@@ -9803,7 +9784,7 @@
     <row r="8" spans="1:140" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="21"/>
       <c r="B8" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C8" s="1" t="str">
         <f>Data_base_case!D38</f>
@@ -9814,13 +9795,13 @@
         <v>Used (1 or 0)</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F8" s="1">
         <v>0</v>
       </c>
       <c r="G8" s="20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H8" s="1">
         <f>INDEX(Data_base_case!$D$5:$AA$88,MATCH(Scenarios_definition!C8,Data_base_case!$D$5:$D$88,0),MATCH(Scenarios_definition!D8&amp;Scenarios_definition!G8,Data_base_case!$D$4:$AA$4,0))</f>
@@ -9829,20 +9810,20 @@
     </row>
     <row r="9" spans="1:140" s="29" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="21" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B9" s="29" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D9" s="29" t="str">
         <f>Data_base_case!$R$1</f>
         <v>Load min (% of max capacity)</v>
       </c>
       <c r="E9" s="29" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F9" s="29">
         <v>1</v>
@@ -9858,17 +9839,17 @@
     <row r="10" spans="1:140" s="29" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="21"/>
       <c r="B10" s="29" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C10" s="29" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D10" s="29" t="str">
         <f>Data_base_case!$R$1</f>
         <v>Load min (% of max capacity)</v>
       </c>
       <c r="E10" s="29" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F10" s="29">
         <v>1</v>
@@ -9883,17 +9864,17 @@
     </row>
     <row r="11" spans="1:140" s="29" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="23" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C11" s="23" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D11" s="23" t="str">
         <f>Data_base_case!$R$1</f>
         <v>Load min (% of max capacity)</v>
       </c>
       <c r="E11" s="23" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F11" s="23">
         <v>1</v>
@@ -9909,17 +9890,17 @@
     <row r="12" spans="1:140" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A12" s="22"/>
       <c r="B12" s="23" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C12" s="23" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D12" s="23" t="str">
         <f>Data_base_case!$R$1</f>
         <v>Load min (% of max capacity)</v>
       </c>
       <c r="E12" s="23" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F12" s="23">
         <v>1</v>
@@ -9934,20 +9915,20 @@
     </row>
     <row r="13" spans="1:140" s="44" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B13" s="44" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C13" s="44" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D13" s="44" t="str">
         <f>Data_base_case!$R$1</f>
         <v>Load min (% of max capacity)</v>
       </c>
       <c r="E13" s="44" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F13" s="44">
         <v>0</v>
@@ -9962,17 +9943,17 @@
     </row>
     <row r="14" spans="1:140" s="44" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B14" s="44" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C14" s="44" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D14" s="44" t="str">
         <f>Data_base_case!$R$1</f>
         <v>Load min (% of max capacity)</v>
       </c>
       <c r="E14" s="44" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F14" s="44">
         <v>0</v>
@@ -10017,90 +9998,90 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="B1" s="139" t="s">
-        <v>121</v>
-      </c>
-      <c r="C1" s="139"/>
-      <c r="D1" s="139"/>
-      <c r="E1" s="139"/>
-      <c r="F1" s="139"/>
-      <c r="G1" s="139"/>
-      <c r="H1" s="139"/>
-      <c r="I1" s="139"/>
-      <c r="J1" s="139"/>
-      <c r="K1" s="140"/>
+      <c r="B1" s="134" t="s">
+        <v>120</v>
+      </c>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
+      <c r="F1" s="134"/>
+      <c r="G1" s="134"/>
+      <c r="H1" s="134"/>
+      <c r="I1" s="134"/>
+      <c r="J1" s="134"/>
+      <c r="K1" s="135"/>
     </row>
     <row r="2" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="141" t="s">
-        <v>128</v>
-      </c>
-      <c r="C2" s="141" t="s">
-        <v>257</v>
+      <c r="B2" s="136" t="s">
+        <v>127</v>
+      </c>
+      <c r="C2" s="136" t="s">
+        <v>256</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G2" s="2">
         <v>2025</v>
       </c>
-      <c r="H2" s="141" t="s">
-        <v>138</v>
+      <c r="H2" s="136" t="s">
+        <v>137</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="K2" s="59" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="B3" s="141"/>
-      <c r="C3" s="141"/>
+      <c r="B3" s="136"/>
+      <c r="C3" s="136"/>
       <c r="D3" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G3" s="2"/>
-      <c r="H3" s="141"/>
+      <c r="H3" s="136"/>
       <c r="I3" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J3" s="2"/>
       <c r="K3" s="59"/>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="B4" s="141"/>
-      <c r="C4" s="141"/>
+      <c r="B4" s="136"/>
+      <c r="C4" s="136"/>
       <c r="D4" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G4" s="2"/>
-      <c r="H4" s="141"/>
+      <c r="H4" s="136"/>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
       <c r="K4" s="59"/>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="B5" s="141"/>
-      <c r="C5" s="141"/>
+      <c r="B5" s="136"/>
+      <c r="C5" s="136"/>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -10114,7 +10095,7 @@
       <c r="O5" s="3"/>
       <c r="P5" s="28"/>
       <c r="Q5" s="14" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.35">
@@ -10128,55 +10109,55 @@
     </row>
     <row r="7" spans="1:17" s="25" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A7" s="25" t="s">
+        <v>89</v>
+      </c>
+      <c r="B7" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="C7" s="25" t="s">
+        <v>125</v>
+      </c>
+      <c r="D7" s="25" t="s">
+        <v>173</v>
+      </c>
+      <c r="E7" s="25" t="s">
         <v>90</v>
       </c>
-      <c r="B7" s="25" t="s">
-        <v>127</v>
-      </c>
-      <c r="C7" s="25" t="s">
-        <v>126</v>
-      </c>
-      <c r="D7" s="25" t="s">
-        <v>174</v>
-      </c>
-      <c r="E7" s="25" t="s">
+      <c r="F7" s="25" t="s">
+        <v>100</v>
+      </c>
+      <c r="G7" s="25" t="s">
+        <v>136</v>
+      </c>
+      <c r="H7" s="25" t="s">
+        <v>93</v>
+      </c>
+      <c r="I7" s="25" t="s">
         <v>91</v>
       </c>
-      <c r="F7" s="25" t="s">
-        <v>101</v>
-      </c>
-      <c r="G7" s="25" t="s">
-        <v>137</v>
-      </c>
-      <c r="H7" s="25" t="s">
+      <c r="J7" s="25" t="s">
+        <v>92</v>
+      </c>
+      <c r="K7" s="26" t="s">
         <v>94</v>
       </c>
-      <c r="I7" s="25" t="s">
-        <v>92</v>
-      </c>
-      <c r="J7" s="25" t="s">
-        <v>93</v>
-      </c>
-      <c r="K7" s="26" t="s">
+      <c r="L7" s="25" t="s">
         <v>95</v>
       </c>
-      <c r="L7" s="25" t="s">
+      <c r="M7" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="M7" s="25" t="s">
+      <c r="N7" s="25" t="s">
         <v>97</v>
       </c>
-      <c r="N7" s="25" t="s">
+      <c r="O7" s="25" t="s">
+        <v>105</v>
+      </c>
+      <c r="P7" s="26" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q7" s="25" t="s">
         <v>98</v>
-      </c>
-      <c r="O7" s="25" t="s">
-        <v>106</v>
-      </c>
-      <c r="P7" s="26" t="s">
-        <v>107</v>
-      </c>
-      <c r="Q7" s="25" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.35">
@@ -10185,19 +10166,19 @@
         <v>1</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D8" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G8" s="58">
         <v>2025</v>
@@ -10207,16 +10188,16 @@
         <v>2019</v>
       </c>
       <c r="I8" s="14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J8" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K8" s="17" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="L8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="b">
         <v>0</v>
@@ -10240,19 +10221,19 @@
         <v>2</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D9" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G9" s="58">
         <v>2025</v>
@@ -10262,13 +10243,13 @@
         <v>2019</v>
       </c>
       <c r="I9" s="14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K9" s="17" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="L9" t="b">
         <v>0</v>
@@ -10295,19 +10276,19 @@
         <v>3</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G10" s="58">
         <v>2025</v>
@@ -10317,13 +10298,13 @@
         <v>2019</v>
       </c>
       <c r="I10" s="14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K10" s="17" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="L10" t="b">
         <v>0</v>
@@ -10350,19 +10331,19 @@
         <v>4</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D11" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G11" s="58">
         <v>2025</v>
@@ -10372,13 +10353,13 @@
         <v>2019</v>
       </c>
       <c r="I11" s="14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J11" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K11" s="17" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="L11" t="b">
         <v>0</v>
@@ -10405,19 +10386,19 @@
         <v>5</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D12" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G12" s="58">
         <v>2025</v>
@@ -10427,13 +10408,13 @@
         <v>2019</v>
       </c>
       <c r="I12" s="14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J12" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K12" s="17" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="L12" t="b">
         <v>0</v>
@@ -10460,19 +10441,19 @@
         <v>6</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D13" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F13" s="14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G13" s="58">
         <v>2025</v>
@@ -10482,13 +10463,13 @@
         <v>2019</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J13" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K13" s="17" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="L13" t="b">
         <v>0</v>
@@ -10515,19 +10496,19 @@
         <v>7</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D14" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F14" s="14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G14" s="58">
         <v>2025</v>
@@ -10537,13 +10518,13 @@
         <v>2019</v>
       </c>
       <c r="I14" s="14" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J14" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K14" s="17" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="L14" t="b">
         <v>0</v>
@@ -10570,19 +10551,19 @@
         <v>8</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D15" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F15" s="14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G15" s="58">
         <v>2025</v>
@@ -10592,13 +10573,13 @@
         <v>2019</v>
       </c>
       <c r="I15" s="14" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J15" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K15" s="17" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="L15" t="b">
         <v>0</v>
@@ -10625,19 +10606,19 @@
         <v>9</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D16" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F16" s="14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G16" s="58">
         <v>2025</v>
@@ -10647,13 +10628,13 @@
         <v>2019</v>
       </c>
       <c r="I16" s="14" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J16" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K16" s="17" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="L16" t="b">
         <v>0</v>
@@ -10680,19 +10661,19 @@
         <v>10</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D17" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F17" s="14" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G17" s="58">
         <v>2025</v>
@@ -10702,13 +10683,13 @@
         <v>2019</v>
       </c>
       <c r="I17" s="14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J17" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K17" s="17" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="L17" t="b">
         <v>0</v>
@@ -10735,19 +10716,19 @@
         <v>11</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D18" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F18" s="14" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G18" s="58">
         <v>2025</v>
@@ -10757,13 +10738,13 @@
         <v>2019</v>
       </c>
       <c r="I18" s="14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J18" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K18" s="17" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="L18" t="b">
         <v>0</v>
@@ -10790,19 +10771,19 @@
         <v>12</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D19" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F19" s="14" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G19" s="58">
         <v>2025</v>
@@ -10812,13 +10793,13 @@
         <v>2019</v>
       </c>
       <c r="I19" s="14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J19" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K19" s="17" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="L19" t="b">
         <v>0</v>
@@ -10845,19 +10826,19 @@
         <v>13</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D20" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F20" s="14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G20" s="58">
         <v>2025</v>
@@ -10867,13 +10848,13 @@
         <v>2019</v>
       </c>
       <c r="I20" s="14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J20" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K20" s="17" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="L20" t="b">
         <v>0</v>
@@ -10900,19 +10881,19 @@
         <v>14</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D21" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F21" s="14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G21" s="58">
         <v>2025</v>
@@ -10922,13 +10903,13 @@
         <v>2019</v>
       </c>
       <c r="I21" s="14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J21" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K21" s="17" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="L21" t="b">
         <v>0</v>
@@ -10955,19 +10936,19 @@
         <v>15</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D22" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F22" s="14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G22" s="58">
         <v>2025</v>
@@ -10977,13 +10958,13 @@
         <v>2019</v>
       </c>
       <c r="I22" s="14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J22" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K22" s="17" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="L22" t="b">
         <v>0</v>
@@ -11010,19 +10991,19 @@
         <v>16</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D23" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F23" s="14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G23" s="58">
         <v>2025</v>
@@ -11032,13 +11013,13 @@
         <v>2019</v>
       </c>
       <c r="I23" s="14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J23" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K23" s="17" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="L23" t="b">
         <v>0</v>
@@ -11065,19 +11046,19 @@
         <v>17</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D24" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F24" s="14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G24" s="58">
         <v>2025</v>
@@ -11087,13 +11068,13 @@
         <v>2019</v>
       </c>
       <c r="I24" s="14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J24" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K24" s="17" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="L24" t="b">
         <v>0</v>
@@ -11120,19 +11101,19 @@
         <v>18</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D25" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F25" s="14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G25" s="58">
         <v>2025</v>
@@ -11142,13 +11123,13 @@
         <v>2019</v>
       </c>
       <c r="I25" s="14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J25" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K25" s="17" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="L25" t="b">
         <v>0</v>
@@ -11175,19 +11156,19 @@
         <v>19</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D26" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F26" s="14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G26" s="58">
         <v>2025</v>
@@ -11197,13 +11178,13 @@
         <v>2019</v>
       </c>
       <c r="I26" s="14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J26" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K26" s="17" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="L26" t="b">
         <v>0</v>
@@ -11230,19 +11211,19 @@
         <v>20</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D27" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E27" s="14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F27" s="14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G27" s="58">
         <v>2025</v>
@@ -11252,13 +11233,13 @@
         <v>2019</v>
       </c>
       <c r="I27" s="14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J27" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K27" s="17" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="L27" t="b">
         <v>0</v>
@@ -11285,19 +11266,19 @@
         <v>21</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D28" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E28" s="14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F28" s="14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G28" s="58">
         <v>2025</v>
@@ -11307,13 +11288,13 @@
         <v>2019</v>
       </c>
       <c r="I28" s="14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J28" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K28" s="17" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="L28" t="b">
         <v>0</v>
@@ -11369,66 +11350,66 @@
   <sheetData>
     <row r="1" spans="1:8" s="33" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="33" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B1" s="56" t="s">
+        <v>145</v>
+      </c>
+      <c r="C1" s="56" t="s">
+        <v>165</v>
+      </c>
+      <c r="D1" s="56" t="s">
+        <v>83</v>
+      </c>
+      <c r="E1" s="56" t="s">
+        <v>144</v>
+      </c>
+      <c r="F1" s="56" t="s">
         <v>146</v>
       </c>
-      <c r="C1" s="56" t="s">
-        <v>166</v>
-      </c>
-      <c r="D1" s="56" t="s">
-        <v>84</v>
-      </c>
-      <c r="E1" s="56" t="s">
-        <v>145</v>
-      </c>
-      <c r="F1" s="56" t="s">
-        <v>147</v>
-      </c>
       <c r="G1" s="34" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H1" s="33" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="55" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B2" s="54" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C2" s="54" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D2" s="54">
         <v>2023</v>
       </c>
       <c r="E2" s="54" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G2" s="32"/>
       <c r="H2" s="37" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="55" t="s">
+        <v>193</v>
+      </c>
+      <c r="B3" s="54" t="s">
         <v>194</v>
       </c>
-      <c r="B3" s="54" t="s">
+      <c r="C3" s="54" t="s">
         <v>195</v>
-      </c>
-      <c r="C3" s="54" t="s">
-        <v>196</v>
       </c>
       <c r="D3" s="54">
         <v>2023</v>
       </c>
       <c r="E3" s="54" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G3" s="32"/>
     </row>
@@ -11438,19 +11419,19 @@
         <v>Adams2019</v>
       </c>
       <c r="B4" s="54" t="s">
+        <v>199</v>
+      </c>
+      <c r="C4" s="54" t="s">
         <v>200</v>
-      </c>
-      <c r="C4" s="54" t="s">
-        <v>201</v>
       </c>
       <c r="D4" s="54">
         <v>2019</v>
       </c>
       <c r="E4" s="54" t="s">
+        <v>201</v>
+      </c>
+      <c r="G4" s="32" t="s">
         <v>202</v>
-      </c>
-      <c r="G4" s="32" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
@@ -11459,19 +11440,19 @@
         <v>Papadias2021</v>
       </c>
       <c r="B5" s="55" t="s">
+        <v>203</v>
+      </c>
+      <c r="C5" s="54" t="s">
         <v>204</v>
-      </c>
-      <c r="C5" s="54" t="s">
-        <v>205</v>
       </c>
       <c r="D5" s="54">
         <v>2021</v>
       </c>
       <c r="E5" s="54" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G5" s="32" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -11480,19 +11461,19 @@
         <v>Armijo2020</v>
       </c>
       <c r="B6" s="54" t="s">
+        <v>206</v>
+      </c>
+      <c r="C6" s="54" t="s">
         <v>207</v>
-      </c>
-      <c r="C6" s="54" t="s">
-        <v>208</v>
       </c>
       <c r="D6" s="54">
         <v>2020</v>
       </c>
       <c r="E6" s="54" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G6" s="32" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
@@ -11501,80 +11482,80 @@
         <v>IEA2019</v>
       </c>
       <c r="B7" s="54" t="s">
+        <v>209</v>
+      </c>
+      <c r="C7" s="54" t="s">
         <v>210</v>
-      </c>
-      <c r="C7" s="54" t="s">
-        <v>211</v>
       </c>
       <c r="D7" s="54">
         <v>2019</v>
       </c>
       <c r="E7" s="54" t="s">
+        <v>211</v>
+      </c>
+      <c r="G7" s="32" t="s">
         <v>212</v>
-      </c>
-      <c r="G7" s="32" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="31" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="55" t="s">
+        <v>213</v>
+      </c>
+      <c r="B8" s="54" t="s">
         <v>214</v>
       </c>
-      <c r="B8" s="54" t="s">
+      <c r="C8" s="54" t="s">
         <v>215</v>
-      </c>
-      <c r="C8" s="54" t="s">
-        <v>216</v>
       </c>
       <c r="D8" s="54">
         <v>2023</v>
       </c>
       <c r="E8" s="54" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G8" s="32" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="55" t="s">
+        <v>217</v>
+      </c>
+      <c r="B9" s="57" t="s">
         <v>218</v>
       </c>
-      <c r="B9" s="57" t="s">
+      <c r="C9" s="54" t="s">
         <v>219</v>
-      </c>
-      <c r="C9" s="54" t="s">
-        <v>220</v>
       </c>
       <c r="D9" s="54">
         <v>2023</v>
       </c>
       <c r="E9" s="54" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G9" s="32"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="55" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B10" s="54" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C10" s="54" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D10" s="54">
         <v>2020</v>
       </c>
       <c r="E10" s="54" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G10" s="32" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H10" s="55" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -11583,59 +11564,59 @@
         <v>Ikäheimo2018</v>
       </c>
       <c r="B11" s="54" t="s">
+        <v>226</v>
+      </c>
+      <c r="C11" s="54" t="s">
         <v>227</v>
-      </c>
-      <c r="C11" s="54" t="s">
-        <v>228</v>
       </c>
       <c r="D11" s="54">
         <v>2018</v>
       </c>
       <c r="E11" s="54" t="s">
+        <v>228</v>
+      </c>
+      <c r="G11" s="32" t="s">
         <v>229</v>
-      </c>
-      <c r="G11" s="32" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="55" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B12" s="54" t="s">
+        <v>230</v>
+      </c>
+      <c r="C12" s="54" t="s">
         <v>231</v>
-      </c>
-      <c r="C12" s="54" t="s">
-        <v>232</v>
       </c>
       <c r="D12" s="54">
         <v>2020</v>
       </c>
       <c r="E12" s="54" t="s">
+        <v>232</v>
+      </c>
+      <c r="G12" s="32" t="s">
         <v>233</v>
-      </c>
-      <c r="G12" s="32" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="55" t="s">
+        <v>235</v>
+      </c>
+      <c r="B13" s="55" t="s">
         <v>236</v>
       </c>
-      <c r="B13" s="55" t="s">
-        <v>237</v>
-      </c>
       <c r="C13" s="54" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D13" s="54">
         <v>2021</v>
       </c>
       <c r="E13" s="54" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G13" s="32" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
@@ -11935,101 +11916,101 @@
     </row>
     <row r="114" spans="2:7" x14ac:dyDescent="0.35">
       <c r="G114" s="32" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="117" spans="2:7" x14ac:dyDescent="0.35">
       <c r="G117" s="32" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="118" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B118" s="2"/>
       <c r="C118" s="2"/>
       <c r="G118" s="38" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="120" spans="2:7" x14ac:dyDescent="0.35">
       <c r="G120" s="32" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="124" spans="2:7" x14ac:dyDescent="0.35">
       <c r="G124" s="32" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="126" spans="2:7" x14ac:dyDescent="0.35">
       <c r="G126" s="32" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="127" spans="2:7" x14ac:dyDescent="0.35">
       <c r="G127" s="32" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="128" spans="2:7" x14ac:dyDescent="0.35">
       <c r="G128" s="32" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="129" spans="2:7" x14ac:dyDescent="0.35">
       <c r="G129" s="32" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="130" spans="2:7" x14ac:dyDescent="0.35">
       <c r="G130" s="32" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="131" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B131" s="55"/>
       <c r="G131" s="32" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="132" spans="2:7" x14ac:dyDescent="0.35">
       <c r="G132" s="32" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="133" spans="2:7" x14ac:dyDescent="0.35">
       <c r="G133" s="32" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="134" spans="2:7" x14ac:dyDescent="0.35">
       <c r="G134" s="32" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="135" spans="2:7" x14ac:dyDescent="0.35">
       <c r="G135" s="32" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="136" spans="2:7" x14ac:dyDescent="0.35">
       <c r="G136" s="32" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="137" spans="2:7" x14ac:dyDescent="0.35">
       <c r="G137" s="32" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="138" spans="2:7" x14ac:dyDescent="0.35">
       <c r="G138" s="32" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="139" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B139" s="2"/>
       <c r="G139" s="32" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
   </sheetData>
